--- a/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/kyriba_rollout_plan.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/kyriba_rollout_plan.xlsx
@@ -502,12 +502,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -537,26 +537,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cash visibility</t>
+          <t>Liquidity</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Liquidity</t>
+          <t>Cash visibility</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -607,26 +607,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2027-03-12</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Cash visibility</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
